--- a/artfynd/A 34164-2023 artfynd.xlsx
+++ b/artfynd/A 34164-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114046486</v>
+        <v>137521053</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>92149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storkroken-Holmsvattensel, Nb</t>
+          <t>Storåholm, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>785562</v>
+        <v>785625</v>
       </c>
       <c r="R2" t="n">
-        <v>7362566</v>
+        <v>7362590</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-22</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-22</t>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,24 +775,24 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Robert Sandberg</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Frédéric Forsmark</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114046486</t>
+          <t>https://artportalen.se/Sighting/137521053</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114046489</v>
+        <v>114046486</v>
       </c>
       <c r="B3" t="n">
         <v>79327</v>
@@ -817,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>785561</v>
+        <v>785562</v>
       </c>
       <c r="R3" t="n">
-        <v>7362651</v>
+        <v>7362566</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,38 +888,38 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114046489</t>
+          <t>https://artportalen.se/Sighting/114046486</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114046487</v>
+        <v>114046489</v>
       </c>
       <c r="B4" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>785546</v>
+        <v>785561</v>
       </c>
       <c r="R4" t="n">
-        <v>7362561</v>
+        <v>7362651</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,7 +990,1841 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/114046489</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>137521049</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79536</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Storåholm, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>785612</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7362568</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137521049</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>137521055</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79536</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Storåholm, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>785623</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7362594</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137521055</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137521059</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79536</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Storåholm, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>785653</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7362645</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137521059</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137521050</v>
+      </c>
+      <c r="B8" t="n">
+        <v>83527</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Storåholm, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>785620</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7362576</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137521050</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137521060</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Storåholm, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>785657</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7362657</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137521060</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137521071</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Storåholm, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>785681</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7362490</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137521071</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137521072</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Storåholm, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>785595</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7362526</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137521072</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>114046487</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Storkroken-Holmsvattensel, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>785546</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7362561</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-10-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-10-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Robert Sandberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Frédéric Forsmark</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/114046487</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137521045</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Storåholm, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>785643</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7362484</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Barkfläk</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137521045</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137521054</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Storåholm, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>785625</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7362590</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Barkfläk</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137521054</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137521057</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Storåholm, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>785630</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7362615</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Barkfläk</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137521057</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137521058</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Storåholm, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>785643</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7362635</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Barkfläk</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137521058</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137521078</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Storåholm, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>785503</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7362519</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137521078</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137521079</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58035</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Storåholm, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>785515</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7362500</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137521079</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137521051</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58196</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Storåholm, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>785624</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7362585</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137521051</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137521069</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58196</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Storåholm, Nb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>785751</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7362509</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137521069</t>
         </is>
       </c>
     </row>
@@ -989,6 +2833,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34164-2023 artfynd.xlsx
+++ b/artfynd/A 34164-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137521053</v>
       </c>
       <c r="B2" t="n">
-        <v>92149</v>
+        <v>92152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>137521049</v>
       </c>
       <c r="B5" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>137521055</v>
       </c>
       <c r="B6" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>137521059</v>
       </c>
       <c r="B7" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>137521050</v>
       </c>
       <c r="B8" t="n">
-        <v>83527</v>
+        <v>83530</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>137521060</v>
       </c>
       <c r="B9" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>137521071</v>
       </c>
       <c r="B10" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>137521072</v>
       </c>
       <c r="B11" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>137521045</v>
       </c>
       <c r="B13" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>137521054</v>
       </c>
       <c r="B14" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         <v>137521057</v>
       </c>
       <c r="B15" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>137521058</v>
       </c>
       <c r="B16" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>137521078</v>
       </c>
       <c r="B17" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>137521079</v>
       </c>
       <c r="B18" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         <v>137521051</v>
       </c>
       <c r="B19" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>137521069</v>
       </c>
       <c r="B20" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
